--- a/InputData/elec/DCpUC/Decommissioning Cost per Unit Cap.xlsx
+++ b/InputData/elec/DCpUC/Decommissioning Cost per Unit Cap.xlsx
@@ -1,32 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\elec\DCpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI\InputData\elec\DCpUC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_62ECBED3A009106AE4B91D0E082DA4247697AD09" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13005" yWindow="990" windowWidth="15645" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="DCpUC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -200,7 +193,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -560,7 +553,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -693,9 +686,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B7" r:id="rId1"/>
+    <hyperlink ref="B14" r:id="rId2"/>
+    <hyperlink ref="B21" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -703,7 +696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -902,7 +895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
@@ -1071,49 +1064,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1121,24 +1097,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1157,70 +1194,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1322,40 +1312,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A2BD8B8-4AF5-4F12-9D78-EE71E32BA6BC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B4AA6D7-09EE-43D0-92EE-D68F9413456C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63A48F5A-6548-477C-80A4-1AD985453F73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{179437DE-D8E8-4542-B35B-80550A0DF58B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95B41EEA-972B-46DD-94A1-1A975F5BC3E5}"/>
 </file>